--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-los-rios.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1723-493-CM26</t>
+          <t>926853-28-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,6 +569,189 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>1284.84</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1079694-222-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2666.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2906-217-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>26632.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1723-493-CM26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>1056.54</v>
       </c>
     </row>
